--- a/DataTable/AllyUnitDataTable.xlsx
+++ b/DataTable/AllyUnitDataTable.xlsx
@@ -1,17 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Documents\GitHub\pin-ball\DataTable\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D166F4-4A2A-4AA0-9FAC-8F56C7913D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="3075" yWindow="3075" windowWidth="21840" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Common" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="BasicStatus" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="ClassStatus" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="Skill" sheetId="4" r:id="rId7"/>
-    <sheet state="visible" name="SkillDetail" sheetId="5" r:id="rId8"/>
+    <sheet name="Common" sheetId="1" r:id="rId1"/>
+    <sheet name="BasicStatus" sheetId="2" r:id="rId2"/>
+    <sheet name="ClassStatus" sheetId="3" r:id="rId3"/>
+    <sheet name="Skill" sheetId="4" r:id="rId4"/>
+    <sheet name="SkillDetail" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="q7Q/G3Lc0f+6VWUNZz0IOXzpuDZgaQYbq9KKgx4FXyg="/>
     </ext>
@@ -20,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="157">
   <si>
     <t>공통 규칙 테이블</t>
   </si>
@@ -508,43 +520,63 @@
   <si>
     <t>자신 포함 반경 {0}타일 아군 {1}초동안 넉백 면역</t>
   </si>
+  <si>
+    <t>값</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="15.0"/>
+      <sz val="15"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="20.0"/>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
-    <font/>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -584,33 +616,34 @@
     </fill>
   </fills>
   <borders count="27">
-    <border/>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -619,28 +652,48 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -655,17 +708,20 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -680,8 +736,10 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -691,6 +749,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -705,6 +764,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -719,11 +779,16 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -738,8 +803,10 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -749,6 +816,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -760,6 +828,8 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -771,6 +841,8 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -785,6 +857,7 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -799,17 +872,20 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -824,22 +900,29 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -848,19 +931,25 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -870,255 +959,254 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+  <cellXfs count="74">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="8" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="9" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="15" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="17" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="18" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="19" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="15" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="20" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="21" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="19" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="22" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="21" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="21" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="12" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="25" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="26" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="21" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="17" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="17" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="19" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1308,176 +1396,180 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="2.63"/>
-    <col customWidth="1" min="2" max="2" width="25.13"/>
-    <col customWidth="1" min="3" max="3" width="21.13"/>
-    <col customWidth="1" min="4" max="4" width="15.13"/>
-    <col customWidth="1" min="5" max="5" width="2.63"/>
+    <col min="1" max="1" width="2.625" customWidth="1"/>
+    <col min="2" max="2" width="25.125" customWidth="1"/>
+    <col min="3" max="3" width="21.125" customWidth="1"/>
+    <col min="4" max="4" width="15.125" customWidth="1"/>
+    <col min="5" max="5" width="2.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2"/>
       <c r="E1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" ht="19.5" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="57" t="s">
         <v>0</v>
       </c>
+      <c r="C2" s="58"/>
       <c r="D2" s="2"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5" ht="26.25" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
       <c r="D3" s="2"/>
       <c r="E3" s="1"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="8"/>
-    </row>
-    <row r="5" ht="77.25" customHeight="1">
+      <c r="D4" s="73" t="s">
+        <v>156</v>
+      </c>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="8"/>
-    </row>
-    <row r="6">
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="8"/>
-    </row>
-    <row r="7">
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="10" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="1"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="23">
-        <v>10.0</v>
-      </c>
-      <c r="E8" s="24"/>
-    </row>
-    <row r="9">
+      <c r="D8" s="14">
+        <v>10</v>
+      </c>
+      <c r="E8" s="15"/>
+    </row>
+    <row r="9" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="23">
-        <v>5.0</v>
-      </c>
-      <c r="E9" s="24"/>
-    </row>
-    <row r="10">
+      <c r="D9" s="14">
+        <v>5</v>
+      </c>
+      <c r="E9" s="15"/>
+    </row>
+    <row r="10" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="E10" s="24"/>
-    </row>
-    <row r="11">
+      <c r="D10" s="14">
+        <v>0</v>
+      </c>
+      <c r="E10" s="15"/>
+    </row>
+    <row r="11" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="29">
-        <v>12.0</v>
-      </c>
-      <c r="E11" s="24"/>
-    </row>
-    <row r="12">
+      <c r="D11" s="19">
+        <v>12</v>
+      </c>
+      <c r="E11" s="15"/>
+    </row>
+    <row r="12" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="29">
-        <v>4.0</v>
-      </c>
-      <c r="E12" s="24"/>
-    </row>
-    <row r="13">
+      <c r="D12" s="19">
+        <v>4</v>
+      </c>
+      <c r="E12" s="15"/>
+    </row>
+    <row r="13" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="22">
         <v>0.5</v>
       </c>
-      <c r="E13" s="24"/>
-    </row>
-    <row r="14">
+      <c r="E13" s="15"/>
+    </row>
+    <row r="14" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="34"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1486,29 +1578,30 @@
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:D5"/>
   </mergeCells>
-  <printOptions gridLines="1" horizontalCentered="1"/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup fitToHeight="0" paperSize="9" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <printOptions horizontalCentered="1" gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:O12"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="2.63"/>
-    <col customWidth="1" min="4" max="4" width="21.13"/>
-    <col customWidth="1" min="11" max="13" width="12.63"/>
-    <col customWidth="1" min="14" max="14" width="15.13"/>
-    <col customWidth="1" min="15" max="15" width="2.63"/>
+    <col min="1" max="1" width="2.625" customWidth="1"/>
+    <col min="4" max="4" width="21.125" customWidth="1"/>
+    <col min="11" max="13" width="12.625" customWidth="1"/>
+    <col min="14" max="14" width="15.125" customWidth="1"/>
+    <col min="15" max="15" width="2.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1525,11 +1618,13 @@
       <c r="N1" s="2"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:15" ht="19.5" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="57" t="s">
         <v>4</v>
       </c>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -1542,11 +1637,11 @@
       <c r="N2" s="2"/>
       <c r="O2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:15" ht="26.25" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -1559,344 +1654,339 @@
       <c r="N3" s="2"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="61" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="O4" s="8"/>
-    </row>
-    <row r="5" ht="77.25" customHeight="1">
+      <c r="O4" s="4"/>
+    </row>
+    <row r="5" spans="1:15" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="8"/>
-    </row>
-    <row r="6">
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="60"/>
+      <c r="L5" s="60"/>
+      <c r="M5" s="60"/>
+      <c r="N5" s="60"/>
+      <c r="O5" s="4"/>
+    </row>
+    <row r="6" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="12" t="s">
+      <c r="C6" s="63"/>
+      <c r="D6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K6" s="13" t="s">
+      <c r="K6" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="L6" s="13" t="s">
+      <c r="L6" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M6" s="13" t="s">
+      <c r="M6" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="N6" s="13" t="s">
+      <c r="N6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O6" s="8"/>
-    </row>
-    <row r="7">
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="25"/>
-      <c r="D7" s="16" t="s">
+      <c r="C7" s="65"/>
+      <c r="D7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="26" t="s">
+      <c r="H7" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="I7" s="26" t="s">
+      <c r="I7" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="J7" s="26" t="s">
+      <c r="J7" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="K7" s="37" t="s">
+      <c r="K7" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="L7" s="37" t="s">
+      <c r="L7" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="M7" s="37" t="s">
+      <c r="M7" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="N7" s="18" t="s">
+      <c r="N7" s="10" t="s">
         <v>69</v>
       </c>
       <c r="O7" s="1"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="E8" s="42">
-        <v>180.0</v>
-      </c>
-      <c r="F8" s="42">
-        <v>18.0</v>
-      </c>
-      <c r="G8" s="42">
-        <v>10.0</v>
-      </c>
-      <c r="H8" s="42">
+      <c r="E8" s="32">
+        <v>180</v>
+      </c>
+      <c r="F8" s="32">
+        <v>18</v>
+      </c>
+      <c r="G8" s="32">
+        <v>10</v>
+      </c>
+      <c r="H8" s="32">
         <v>2.5</v>
       </c>
-      <c r="I8" s="43">
+      <c r="I8" s="33">
         <v>0.85</v>
       </c>
-      <c r="J8" s="43">
-        <v>1.1</v>
-      </c>
-      <c r="K8" s="44">
-        <v>24.0</v>
-      </c>
-      <c r="L8" s="44">
-        <v>3.0</v>
-      </c>
-      <c r="M8" s="44">
-        <v>2.0</v>
-      </c>
-      <c r="N8" s="23">
+      <c r="J8" s="33">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="K8" s="34">
+        <v>24</v>
+      </c>
+      <c r="L8" s="34">
+        <v>3</v>
+      </c>
+      <c r="M8" s="34">
+        <v>2</v>
+      </c>
+      <c r="N8" s="14">
         <v>0.03</v>
       </c>
-      <c r="O8" s="24"/>
-    </row>
-    <row r="9">
+      <c r="O8" s="15"/>
+    </row>
+    <row r="9" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="E9" s="42">
-        <v>110.0</v>
-      </c>
-      <c r="F9" s="42">
-        <v>16.0</v>
-      </c>
-      <c r="G9" s="42">
-        <v>4.0</v>
-      </c>
-      <c r="H9" s="42">
+      <c r="E9" s="32">
+        <v>110</v>
+      </c>
+      <c r="F9" s="32">
+        <v>16</v>
+      </c>
+      <c r="G9" s="32">
+        <v>4</v>
+      </c>
+      <c r="H9" s="32">
         <v>2.8</v>
       </c>
-      <c r="I9" s="43">
-        <v>1.1</v>
-      </c>
-      <c r="J9" s="43">
+      <c r="I9" s="33">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J9" s="33">
         <v>5.5</v>
       </c>
-      <c r="K9" s="44">
-        <v>15.0</v>
-      </c>
-      <c r="L9" s="44">
-        <v>3.0</v>
-      </c>
-      <c r="M9" s="44">
-        <v>1.0</v>
-      </c>
-      <c r="N9" s="23">
+      <c r="K9" s="34">
+        <v>15</v>
+      </c>
+      <c r="L9" s="34">
+        <v>3</v>
+      </c>
+      <c r="M9" s="34">
+        <v>1</v>
+      </c>
+      <c r="N9" s="14">
         <v>0.04</v>
       </c>
-      <c r="O9" s="24"/>
-    </row>
-    <row r="10">
+      <c r="O9" s="15"/>
+    </row>
+    <row r="10" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="E10" s="42">
-        <v>95.0</v>
-      </c>
-      <c r="F10" s="42">
-        <v>21.0</v>
-      </c>
-      <c r="G10" s="42">
-        <v>3.0</v>
-      </c>
-      <c r="H10" s="42">
+      <c r="E10" s="32">
+        <v>95</v>
+      </c>
+      <c r="F10" s="32">
+        <v>21</v>
+      </c>
+      <c r="G10" s="32">
+        <v>3</v>
+      </c>
+      <c r="H10" s="32">
         <v>2.5</v>
       </c>
-      <c r="I10" s="43">
+      <c r="I10" s="33">
         <v>0.72</v>
       </c>
-      <c r="J10" s="43">
-        <v>5.0</v>
-      </c>
-      <c r="K10" s="44">
-        <v>13.0</v>
-      </c>
-      <c r="L10" s="44">
-        <v>4.0</v>
-      </c>
-      <c r="M10" s="44">
-        <v>1.0</v>
-      </c>
-      <c r="N10" s="23">
+      <c r="J10" s="33">
+        <v>5</v>
+      </c>
+      <c r="K10" s="34">
+        <v>13</v>
+      </c>
+      <c r="L10" s="34">
+        <v>4</v>
+      </c>
+      <c r="M10" s="34">
+        <v>1</v>
+      </c>
+      <c r="N10" s="14">
         <v>0.02</v>
       </c>
-      <c r="O10" s="24"/>
-    </row>
-    <row r="11">
+      <c r="O10" s="15"/>
+    </row>
+    <row r="11" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="D11" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="E11" s="58">
-        <v>150.0</v>
-      </c>
-      <c r="F11" s="58">
-        <v>17.0</v>
-      </c>
-      <c r="G11" s="58">
-        <v>7.0</v>
-      </c>
-      <c r="H11" s="58">
+      <c r="E11" s="46">
+        <v>150</v>
+      </c>
+      <c r="F11" s="46">
+        <v>17</v>
+      </c>
+      <c r="G11" s="46">
+        <v>7</v>
+      </c>
+      <c r="H11" s="46">
         <v>2.7</v>
       </c>
-      <c r="I11" s="60">
+      <c r="I11" s="48">
         <v>0.95</v>
       </c>
-      <c r="J11" s="60">
-        <v>2.2</v>
-      </c>
-      <c r="K11" s="64">
-        <v>20.0</v>
-      </c>
-      <c r="L11" s="64">
-        <v>3.0</v>
-      </c>
-      <c r="M11" s="64">
-        <v>2.0</v>
-      </c>
-      <c r="N11" s="32">
+      <c r="J11" s="48">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K11" s="50">
+        <v>20</v>
+      </c>
+      <c r="L11" s="50">
+        <v>3</v>
+      </c>
+      <c r="M11" s="50">
+        <v>2</v>
+      </c>
+      <c r="N11" s="22">
         <v>0.03</v>
       </c>
-      <c r="O11" s="24"/>
-    </row>
-    <row r="12">
+      <c r="O11" s="15"/>
+    </row>
+    <row r="12" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="34"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="24"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
-      <c r="N12" s="35"/>
-      <c r="O12" s="34"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="B6:C6"/>
@@ -1908,32 +1998,38 @@
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="L4:L5"/>
   </mergeCells>
-  <printOptions gridLines="1" horizontalCentered="1"/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup fitToHeight="0" paperSize="9" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <printOptions horizontalCentered="1" gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:S16"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="2.63"/>
-    <col customWidth="1" min="3" max="3" width="25.13"/>
-    <col customWidth="1" min="4" max="4" width="21.13"/>
-    <col customWidth="1" min="12" max="15" width="12.63"/>
-    <col customWidth="1" min="16" max="17" width="15.13"/>
-    <col customWidth="1" min="18" max="18" width="25.13"/>
-    <col customWidth="1" min="19" max="19" width="2.63"/>
+    <col min="1" max="1" width="2.625" customWidth="1"/>
+    <col min="3" max="3" width="25.125" customWidth="1"/>
+    <col min="4" max="4" width="21.125" customWidth="1"/>
+    <col min="12" max="15" width="12.625" customWidth="1"/>
+    <col min="16" max="17" width="15.125" customWidth="1"/>
+    <col min="18" max="18" width="25.125" customWidth="1"/>
+    <col min="19" max="19" width="2.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:19" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1954,11 +2050,13 @@
       <c r="R1" s="2"/>
       <c r="S1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:19" ht="19.5" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="57" t="s">
         <v>2</v>
       </c>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -1975,11 +2073,11 @@
       <c r="R2" s="2"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:19" ht="26.25" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -1996,651 +2094,660 @@
       <c r="R3" s="2"/>
       <c r="S3" s="1"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:19" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" s="61" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="Q4" s="7" t="s">
+      <c r="Q4" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="R4" s="11" t="s">
+      <c r="R4" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="S4" s="8"/>
-    </row>
-    <row r="5" ht="77.25" customHeight="1">
+      <c r="S4" s="4"/>
+    </row>
+    <row r="5" spans="1:19" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="8"/>
-    </row>
-    <row r="6">
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="60"/>
+      <c r="L5" s="60"/>
+      <c r="M5" s="60"/>
+      <c r="N5" s="60"/>
+      <c r="O5" s="60"/>
+      <c r="P5" s="60"/>
+      <c r="Q5" s="60"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="4"/>
+    </row>
+    <row r="6" spans="1:19" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="12" t="s">
+      <c r="C6" s="63"/>
+      <c r="D6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="L6" s="13" t="s">
+      <c r="L6" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M6" s="13" t="s">
+      <c r="M6" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="N6" s="13" t="s">
+      <c r="N6" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="O6" s="13" t="s">
+      <c r="O6" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="P6" s="13" t="s">
+      <c r="P6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="Q6" s="13" t="s">
+      <c r="Q6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="R6" s="22" t="s">
+      <c r="R6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="S6" s="8"/>
-    </row>
-    <row r="7">
+      <c r="S6" s="4"/>
+    </row>
+    <row r="7" spans="1:19" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="25"/>
-      <c r="D7" s="16" t="s">
+      <c r="C7" s="65"/>
+      <c r="D7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="H7" s="26" t="s">
+      <c r="H7" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="I7" s="26" t="s">
+      <c r="I7" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="J7" s="26" t="s">
+      <c r="J7" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="K7" s="26" t="s">
+      <c r="K7" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="L7" s="37" t="s">
+      <c r="L7" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="M7" s="37" t="s">
+      <c r="M7" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="N7" s="37" t="s">
+      <c r="N7" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="O7" s="37" t="s">
+      <c r="O7" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="P7" s="39" t="s">
+      <c r="P7" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="Q7" s="27" t="s">
+      <c r="Q7" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="R7" s="18" t="s">
+      <c r="R7" s="10" t="s">
         <v>71</v>
       </c>
       <c r="S7" s="1"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:19" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="E8" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="F8" s="42">
-        <v>292.0</v>
-      </c>
-      <c r="G8" s="42">
-        <v>29.0</v>
-      </c>
-      <c r="H8" s="42">
-        <v>22.0</v>
-      </c>
-      <c r="I8" s="42">
+      <c r="F8" s="32">
+        <v>292</v>
+      </c>
+      <c r="G8" s="32">
+        <v>29</v>
+      </c>
+      <c r="H8" s="32">
+        <v>22</v>
+      </c>
+      <c r="I8" s="32">
         <v>2.4</v>
       </c>
-      <c r="J8" s="43">
+      <c r="J8" s="33">
         <v>0.89</v>
       </c>
-      <c r="K8" s="43">
-        <v>1.1</v>
-      </c>
-      <c r="L8" s="44">
-        <v>60.0</v>
-      </c>
-      <c r="M8" s="44">
-        <v>30.0</v>
-      </c>
-      <c r="N8" s="44">
-        <v>3.0</v>
-      </c>
-      <c r="O8" s="44">
-        <v>3.0</v>
-      </c>
-      <c r="P8" s="45">
+      <c r="K8" s="33">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L8" s="34">
+        <v>60</v>
+      </c>
+      <c r="M8" s="34">
+        <v>30</v>
+      </c>
+      <c r="N8" s="34">
+        <v>3</v>
+      </c>
+      <c r="O8" s="34">
+        <v>3</v>
+      </c>
+      <c r="P8" s="35">
         <v>0.01</v>
       </c>
-      <c r="Q8" s="20" t="s">
+      <c r="Q8" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="R8" s="30" t="s">
+      <c r="R8" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="S8" s="24"/>
-    </row>
-    <row r="9">
+      <c r="S8" s="15"/>
+    </row>
+    <row r="9" spans="1:19" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="41" t="s">
+      <c r="E9" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="F9" s="42">
-        <v>267.0</v>
-      </c>
-      <c r="G9" s="42">
-        <v>34.0</v>
-      </c>
-      <c r="H9" s="42">
-        <v>14.0</v>
-      </c>
-      <c r="I9" s="42">
+      <c r="F9" s="32">
+        <v>267</v>
+      </c>
+      <c r="G9" s="32">
+        <v>34</v>
+      </c>
+      <c r="H9" s="32">
+        <v>14</v>
+      </c>
+      <c r="I9" s="32">
         <v>2.6</v>
       </c>
-      <c r="J9" s="43">
+      <c r="J9" s="33">
         <v>1.02</v>
       </c>
-      <c r="K9" s="43">
+      <c r="K9" s="33">
         <v>1.2</v>
       </c>
-      <c r="L9" s="44">
-        <v>70.0</v>
-      </c>
-      <c r="M9" s="44">
-        <v>24.0</v>
-      </c>
-      <c r="N9" s="44">
-        <v>5.0</v>
-      </c>
-      <c r="O9" s="44">
-        <v>1.0</v>
-      </c>
-      <c r="P9" s="45">
+      <c r="L9" s="34">
+        <v>70</v>
+      </c>
+      <c r="M9" s="34">
+        <v>24</v>
+      </c>
+      <c r="N9" s="34">
+        <v>5</v>
+      </c>
+      <c r="O9" s="34">
+        <v>1</v>
+      </c>
+      <c r="P9" s="35">
         <v>0.04</v>
       </c>
-      <c r="Q9" s="20" t="s">
+      <c r="Q9" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="R9" s="30" t="s">
+      <c r="R9" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="S9" s="24"/>
-    </row>
-    <row r="10">
+      <c r="S9" s="15"/>
+    </row>
+    <row r="10" spans="1:19" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="E10" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="F10" s="42">
-        <v>175.0</v>
-      </c>
-      <c r="G10" s="42">
-        <v>28.0</v>
-      </c>
-      <c r="H10" s="42">
-        <v>9.0</v>
-      </c>
-      <c r="I10" s="42">
-        <v>3.0</v>
-      </c>
-      <c r="J10" s="43">
+      <c r="F10" s="32">
+        <v>175</v>
+      </c>
+      <c r="G10" s="32">
+        <v>28</v>
+      </c>
+      <c r="H10" s="32">
+        <v>9</v>
+      </c>
+      <c r="I10" s="32">
+        <v>3</v>
+      </c>
+      <c r="J10" s="33">
         <v>1.28</v>
       </c>
-      <c r="K10" s="43">
+      <c r="K10" s="33">
         <v>5.2</v>
       </c>
-      <c r="L10" s="44">
-        <v>70.0</v>
-      </c>
-      <c r="M10" s="44">
-        <v>18.0</v>
-      </c>
-      <c r="N10" s="44">
-        <v>3.0</v>
-      </c>
-      <c r="O10" s="44">
-        <v>1.0</v>
-      </c>
-      <c r="P10" s="45">
+      <c r="L10" s="34">
+        <v>70</v>
+      </c>
+      <c r="M10" s="34">
+        <v>18</v>
+      </c>
+      <c r="N10" s="34">
+        <v>3</v>
+      </c>
+      <c r="O10" s="34">
+        <v>1</v>
+      </c>
+      <c r="P10" s="35">
         <v>0.04</v>
       </c>
-      <c r="Q10" s="20" t="s">
+      <c r="Q10" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="R10" s="30" t="s">
+      <c r="R10" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="S10" s="24"/>
-    </row>
-    <row r="11">
+      <c r="S10" s="15"/>
+    </row>
+    <row r="11" spans="1:19" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D11" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="50" t="s">
+      <c r="E11" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="F11" s="51">
-        <v>160.0</v>
-      </c>
-      <c r="G11" s="51">
-        <v>33.0</v>
-      </c>
-      <c r="H11" s="51">
-        <v>7.0</v>
-      </c>
-      <c r="I11" s="51">
+      <c r="F11" s="41">
+        <v>160</v>
+      </c>
+      <c r="G11" s="41">
+        <v>33</v>
+      </c>
+      <c r="H11" s="41">
+        <v>7</v>
+      </c>
+      <c r="I11" s="41">
         <v>2.6</v>
       </c>
-      <c r="J11" s="53">
-        <v>1.15</v>
-      </c>
-      <c r="K11" s="53">
+      <c r="J11" s="42">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K11" s="42">
         <v>6.5</v>
       </c>
-      <c r="L11" s="54">
-        <v>80.0</v>
-      </c>
-      <c r="M11" s="54">
-        <v>12.0</v>
-      </c>
-      <c r="N11" s="54">
-        <v>5.0</v>
-      </c>
-      <c r="O11" s="54">
-        <v>1.0</v>
-      </c>
-      <c r="P11" s="55">
+      <c r="L11" s="43">
+        <v>80</v>
+      </c>
+      <c r="M11" s="43">
+        <v>12</v>
+      </c>
+      <c r="N11" s="43">
+        <v>5</v>
+      </c>
+      <c r="O11" s="43">
+        <v>1</v>
+      </c>
+      <c r="P11" s="44">
         <v>0.02</v>
       </c>
-      <c r="Q11" s="20" t="s">
+      <c r="Q11" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="R11" s="30" t="s">
+      <c r="R11" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="S11" s="24"/>
-    </row>
-    <row r="12">
+      <c r="S11" s="15"/>
+    </row>
+    <row r="12" spans="1:19" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="50" t="s">
+      <c r="E12" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="F12" s="51">
-        <v>144.0</v>
-      </c>
-      <c r="G12" s="51">
-        <v>41.0</v>
-      </c>
-      <c r="H12" s="51">
-        <v>6.0</v>
-      </c>
-      <c r="I12" s="51">
+      <c r="F12" s="41">
+        <v>144</v>
+      </c>
+      <c r="G12" s="41">
+        <v>41</v>
+      </c>
+      <c r="H12" s="41">
+        <v>6</v>
+      </c>
+      <c r="I12" s="41">
         <v>2.4</v>
       </c>
-      <c r="J12" s="53">
+      <c r="J12" s="42">
         <v>0.75</v>
       </c>
-      <c r="K12" s="53">
-        <v>5.0</v>
-      </c>
-      <c r="L12" s="54">
-        <v>80.0</v>
-      </c>
-      <c r="M12" s="54">
-        <v>12.0</v>
-      </c>
-      <c r="N12" s="54">
-        <v>6.0</v>
-      </c>
-      <c r="O12" s="54">
-        <v>1.0</v>
-      </c>
-      <c r="P12" s="55">
+      <c r="K12" s="42">
+        <v>5</v>
+      </c>
+      <c r="L12" s="43">
+        <v>80</v>
+      </c>
+      <c r="M12" s="43">
+        <v>12</v>
+      </c>
+      <c r="N12" s="43">
+        <v>6</v>
+      </c>
+      <c r="O12" s="43">
+        <v>1</v>
+      </c>
+      <c r="P12" s="44">
         <v>0.02</v>
       </c>
-      <c r="Q12" s="20" t="s">
+      <c r="Q12" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="R12" s="30" t="s">
+      <c r="R12" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="S12" s="24"/>
-    </row>
-    <row r="13">
+      <c r="S12" s="15"/>
+    </row>
+    <row r="13" spans="1:19" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="D13" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="E13" s="50" t="s">
+      <c r="E13" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="F13" s="51">
-        <v>159.0</v>
-      </c>
-      <c r="G13" s="51">
-        <v>36.0</v>
-      </c>
-      <c r="H13" s="51">
-        <v>9.0</v>
-      </c>
-      <c r="I13" s="51">
+      <c r="F13" s="41">
+        <v>159</v>
+      </c>
+      <c r="G13" s="41">
+        <v>36</v>
+      </c>
+      <c r="H13" s="41">
+        <v>9</v>
+      </c>
+      <c r="I13" s="41">
         <v>2.5</v>
       </c>
-      <c r="J13" s="53">
+      <c r="J13" s="42">
         <v>0.78</v>
       </c>
-      <c r="K13" s="53">
+      <c r="K13" s="42">
         <v>4.8</v>
       </c>
-      <c r="L13" s="54">
-        <v>75.0</v>
-      </c>
-      <c r="M13" s="54">
-        <v>17.0</v>
-      </c>
-      <c r="N13" s="54">
-        <v>4.0</v>
-      </c>
-      <c r="O13" s="54">
-        <v>2.0</v>
-      </c>
-      <c r="P13" s="55">
+      <c r="L13" s="43">
+        <v>75</v>
+      </c>
+      <c r="M13" s="43">
+        <v>17</v>
+      </c>
+      <c r="N13" s="43">
+        <v>4</v>
+      </c>
+      <c r="O13" s="43">
+        <v>2</v>
+      </c>
+      <c r="P13" s="44">
         <v>0.02</v>
       </c>
-      <c r="Q13" s="20" t="s">
+      <c r="Q13" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="R13" s="30" t="s">
+      <c r="R13" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="S13" s="24"/>
-    </row>
-    <row r="14">
+      <c r="S13" s="15"/>
+    </row>
+    <row r="14" spans="1:19" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="D14" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E14" s="50" t="s">
+      <c r="E14" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="F14" s="51">
-        <v>225.0</v>
-      </c>
-      <c r="G14" s="51">
-        <v>33.0</v>
-      </c>
-      <c r="H14" s="51">
-        <v>14.0</v>
-      </c>
-      <c r="I14" s="51">
+      <c r="F14" s="41">
+        <v>225</v>
+      </c>
+      <c r="G14" s="41">
+        <v>33</v>
+      </c>
+      <c r="H14" s="41">
+        <v>14</v>
+      </c>
+      <c r="I14" s="41">
         <v>3.1</v>
       </c>
-      <c r="J14" s="53">
+      <c r="J14" s="42">
         <v>1.07</v>
       </c>
-      <c r="K14" s="53">
+      <c r="K14" s="42">
         <v>2.4</v>
       </c>
-      <c r="L14" s="54">
-        <v>65.0</v>
-      </c>
-      <c r="M14" s="54">
-        <v>20.0</v>
-      </c>
-      <c r="N14" s="54">
-        <v>5.0</v>
-      </c>
-      <c r="O14" s="54">
-        <v>1.0</v>
-      </c>
-      <c r="P14" s="55">
+      <c r="L14" s="43">
+        <v>65</v>
+      </c>
+      <c r="M14" s="43">
+        <v>20</v>
+      </c>
+      <c r="N14" s="43">
+        <v>5</v>
+      </c>
+      <c r="O14" s="43">
+        <v>1</v>
+      </c>
+      <c r="P14" s="44">
         <v>0.03</v>
       </c>
-      <c r="Q14" s="20" t="s">
+      <c r="Q14" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="R14" s="30" t="s">
+      <c r="R14" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="S14" s="24"/>
-    </row>
-    <row r="15">
+      <c r="S14" s="15"/>
+    </row>
+    <row r="15" spans="1:19" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="D15" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="E15" s="65" t="s">
+      <c r="E15" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="F15" s="58">
-        <v>225.0</v>
-      </c>
-      <c r="G15" s="58">
-        <v>28.0</v>
-      </c>
-      <c r="H15" s="58">
-        <v>20.0</v>
-      </c>
-      <c r="I15" s="58">
-        <v>2.3</v>
-      </c>
-      <c r="J15" s="60">
+      <c r="F15" s="46">
+        <v>225</v>
+      </c>
+      <c r="G15" s="46">
+        <v>28</v>
+      </c>
+      <c r="H15" s="46">
+        <v>20</v>
+      </c>
+      <c r="I15" s="46">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="J15" s="48">
         <v>0.99</v>
       </c>
-      <c r="K15" s="60">
+      <c r="K15" s="48">
         <v>2.5</v>
       </c>
-      <c r="L15" s="64">
-        <v>70.0</v>
-      </c>
-      <c r="M15" s="64">
-        <v>32.0</v>
-      </c>
-      <c r="N15" s="64">
-        <v>3.0</v>
-      </c>
-      <c r="O15" s="64">
-        <v>3.0</v>
-      </c>
-      <c r="P15" s="66">
+      <c r="L15" s="50">
+        <v>70</v>
+      </c>
+      <c r="M15" s="50">
+        <v>32</v>
+      </c>
+      <c r="N15" s="50">
+        <v>3</v>
+      </c>
+      <c r="O15" s="50">
+        <v>3</v>
+      </c>
+      <c r="P15" s="52">
         <v>0.01</v>
       </c>
-      <c r="Q15" s="46" t="s">
+      <c r="Q15" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="R15" s="47" t="s">
+      <c r="R15" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="S15" s="24"/>
-    </row>
-    <row r="16">
+      <c r="S15" s="15"/>
+    </row>
+    <row r="16" spans="1:19" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="34"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="24"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="35"/>
-      <c r="P16" s="35"/>
-      <c r="Q16" s="35"/>
-      <c r="R16" s="35"/>
-      <c r="S16" s="34"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="25"/>
+      <c r="S16" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
     <mergeCell ref="O4:O5"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="Q4:Q5"/>
@@ -2652,40 +2759,32 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
   </mergeCells>
-  <printOptions gridLines="1" horizontalCentered="1"/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup fitToHeight="0" paperSize="9" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <printOptions horizontalCentered="1" gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="2.63"/>
-    <col customWidth="1" min="3" max="3" width="25.13"/>
-    <col customWidth="1" min="4" max="4" width="12.63"/>
-    <col customWidth="1" min="6" max="6" width="15.13"/>
-    <col customWidth="1" min="7" max="7" width="25.13"/>
-    <col customWidth="1" min="8" max="8" width="2.63"/>
+    <col min="1" max="1" width="2.625" customWidth="1"/>
+    <col min="3" max="3" width="25.125" customWidth="1"/>
+    <col min="4" max="4" width="12.625" customWidth="1"/>
+    <col min="6" max="6" width="15.125" customWidth="1"/>
+    <col min="7" max="7" width="25.125" customWidth="1"/>
+    <col min="8" max="8" width="2.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2695,283 +2794,285 @@
       <c r="G1" s="2"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:8" ht="19.5" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="57" t="s">
         <v>1</v>
       </c>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
       <c r="E2" s="1"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:8" ht="26.25" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
       <c r="E3" s="1"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="8"/>
-    </row>
-    <row r="5" ht="77.25" customHeight="1">
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="8"/>
-    </row>
-    <row r="6">
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="12" t="s">
+      <c r="C6" s="63"/>
+      <c r="D6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="8"/>
-    </row>
-    <row r="7">
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="25"/>
-      <c r="D7" s="16" t="s">
+      <c r="C7" s="65"/>
+      <c r="D7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="10" t="s">
         <v>34</v>
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="30" t="s">
+      <c r="G8" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H8" s="24"/>
-    </row>
-    <row r="9">
+      <c r="H8" s="15"/>
+    </row>
+    <row r="9" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="30" t="s">
+      <c r="G9" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="H9" s="24"/>
-    </row>
-    <row r="10">
+      <c r="H9" s="15"/>
+    </row>
+    <row r="10" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="30" t="s">
+      <c r="G10" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="H10" s="24"/>
-    </row>
-    <row r="11">
+      <c r="H10" s="15"/>
+    </row>
+    <row r="11" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C11" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D11" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="38" t="s">
+      <c r="E11" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="30" t="s">
+      <c r="G11" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="H11" s="24"/>
-    </row>
-    <row r="12">
+      <c r="H11" s="15"/>
+    </row>
+    <row r="12" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="E12" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="G12" s="30" t="s">
+      <c r="G12" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="H12" s="24"/>
-    </row>
-    <row r="13">
+      <c r="H12" s="15"/>
+    </row>
+    <row r="13" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="D13" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="E13" s="38" t="s">
+      <c r="E13" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="G13" s="30" t="s">
+      <c r="G13" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="H13" s="24"/>
-    </row>
-    <row r="14">
+      <c r="H13" s="15"/>
+    </row>
+    <row r="14" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="D14" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E14" s="38" t="s">
+      <c r="E14" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="G14" s="30" t="s">
+      <c r="G14" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="H14" s="24"/>
-    </row>
-    <row r="15">
+      <c r="H14" s="15"/>
+    </row>
+    <row r="15" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="D15" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="E15" s="46" t="s">
+      <c r="E15" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="F15" s="46" t="s">
+      <c r="F15" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="G15" s="47" t="s">
+      <c r="G15" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="H15" s="24"/>
-    </row>
-    <row r="16">
+      <c r="H15" s="15"/>
+    </row>
+    <row r="16" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="34"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="24"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="34"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2985,28 +3086,29 @@
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="E4:E5"/>
   </mergeCells>
-  <printOptions gridLines="1" horizontalCentered="1"/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup fitToHeight="0" paperSize="9" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <printOptions horizontalCentered="1" gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:K38"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="2.63"/>
-    <col customWidth="1" min="3" max="4" width="25.13"/>
-    <col customWidth="1" min="5" max="5" width="12.63"/>
-    <col customWidth="1" min="11" max="11" width="2.63"/>
+    <col min="1" max="1" width="2.625" customWidth="1"/>
+    <col min="3" max="4" width="25.125" customWidth="1"/>
+    <col min="5" max="5" width="12.625" customWidth="1"/>
+    <col min="11" max="11" width="2.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3019,11 +3121,14 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" ht="19.5" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="57" t="s">
         <v>91</v>
       </c>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -3031,12 +3136,12 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11" ht="26.25" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -3044,880 +3149,885 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="48" t="s">
+      <c r="F4" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="G4" s="48" t="s">
+      <c r="G4" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="59" t="s">
         <v>102</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="59" t="s">
         <v>102</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="59" t="s">
         <v>102</v>
       </c>
-      <c r="K4" s="8"/>
-    </row>
-    <row r="5" ht="90.0" customHeight="1">
+      <c r="K4" s="4"/>
+    </row>
+    <row r="5" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="49" t="s">
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="G5" s="49" t="s">
+      <c r="G5" s="39" t="s">
         <v>107</v>
       </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="8"/>
-    </row>
-    <row r="6">
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="4"/>
+    </row>
+    <row r="6" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="52"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="12" t="s">
+      <c r="C6" s="72"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K6" s="8"/>
-    </row>
-    <row r="7">
+      <c r="K6" s="4"/>
+    </row>
+    <row r="7" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="16" t="s">
+      <c r="C7" s="65"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="H7" s="26" t="s">
+      <c r="H7" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="I7" s="26" t="s">
+      <c r="I7" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="J7" s="56" t="s">
+      <c r="J7" s="45" t="s">
         <v>118</v>
       </c>
       <c r="K7" s="1"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:11" ht="24" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="57" t="s">
+      <c r="C8" s="70" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="59" t="s">
+      <c r="D8" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G8" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="H8" s="42">
-        <v>160.0</v>
-      </c>
-      <c r="I8" s="42"/>
-      <c r="J8" s="61"/>
-      <c r="K8" s="24"/>
-    </row>
-    <row r="9">
+      <c r="F8" s="32">
+        <v>0</v>
+      </c>
+      <c r="G8" s="32">
+        <v>0</v>
+      </c>
+      <c r="H8" s="32">
+        <v>160</v>
+      </c>
+      <c r="I8" s="32"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="15"/>
+    </row>
+    <row r="9" spans="1:11" ht="24" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
-      <c r="B9" s="62"/>
-      <c r="C9" s="63"/>
-      <c r="D9" s="59" t="s">
+      <c r="B9" s="69"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="47" t="s">
         <v>125</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="42">
-        <v>4.0</v>
-      </c>
-      <c r="G9" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="H9" s="42">
+      <c r="F9" s="32">
+        <v>4</v>
+      </c>
+      <c r="G9" s="32">
+        <v>1</v>
+      </c>
+      <c r="H9" s="32">
         <v>2.5</v>
       </c>
-      <c r="I9" s="42">
-        <v>3.0</v>
-      </c>
-      <c r="J9" s="61"/>
-      <c r="K9" s="24"/>
-    </row>
-    <row r="10">
+      <c r="I9" s="32">
+        <v>3</v>
+      </c>
+      <c r="J9" s="49"/>
+      <c r="K9" s="15"/>
+    </row>
+    <row r="10" spans="1:11" ht="24" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="59" t="s">
+      <c r="B10" s="60"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="47" t="s">
         <v>128</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="G10" s="42">
-        <v>4.0</v>
-      </c>
-      <c r="H10" s="42">
-        <v>5.0</v>
-      </c>
-      <c r="I10" s="42">
-        <v>25.0</v>
-      </c>
-      <c r="J10" s="61"/>
-      <c r="K10" s="24"/>
-    </row>
-    <row r="11">
+      <c r="F10" s="32">
+        <v>1</v>
+      </c>
+      <c r="G10" s="32">
+        <v>4</v>
+      </c>
+      <c r="H10" s="32">
+        <v>5</v>
+      </c>
+      <c r="I10" s="32">
+        <v>25</v>
+      </c>
+      <c r="J10" s="49"/>
+      <c r="K10" s="15"/>
+    </row>
+    <row r="11" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="57" t="s">
+      <c r="C11" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="59" t="s">
+      <c r="D11" s="47" t="s">
         <v>129</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G11" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="H11" s="42">
+      <c r="F11" s="32">
+        <v>0</v>
+      </c>
+      <c r="G11" s="32">
+        <v>1</v>
+      </c>
+      <c r="H11" s="32">
         <v>1.8</v>
       </c>
-      <c r="I11" s="42">
-        <v>180.0</v>
-      </c>
-      <c r="J11" s="61"/>
-      <c r="K11" s="24"/>
-    </row>
-    <row r="12">
+      <c r="I11" s="32">
+        <v>180</v>
+      </c>
+      <c r="J11" s="49"/>
+      <c r="K11" s="15"/>
+    </row>
+    <row r="12" spans="1:11" ht="24" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
-      <c r="B12" s="62"/>
-      <c r="C12" s="63"/>
-      <c r="D12" s="59" t="s">
+      <c r="B12" s="69"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="47" t="s">
         <v>132</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="42">
-        <v>2.0</v>
-      </c>
-      <c r="G12" s="42">
-        <v>4.0</v>
-      </c>
-      <c r="H12" s="42">
-        <v>4.0</v>
-      </c>
-      <c r="I12" s="42">
-        <v>20.0</v>
-      </c>
-      <c r="J12" s="61"/>
-      <c r="K12" s="24"/>
-    </row>
-    <row r="13">
+      <c r="F12" s="32">
+        <v>2</v>
+      </c>
+      <c r="G12" s="32">
+        <v>4</v>
+      </c>
+      <c r="H12" s="32">
+        <v>4</v>
+      </c>
+      <c r="I12" s="32">
+        <v>20</v>
+      </c>
+      <c r="J12" s="49"/>
+      <c r="K12" s="15"/>
+    </row>
+    <row r="13" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="59" t="s">
+      <c r="B13" s="60"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="F13" s="42">
-        <v>3.0</v>
-      </c>
-      <c r="G13" s="42">
-        <v>4.0</v>
-      </c>
-      <c r="H13" s="42">
-        <v>5.0</v>
-      </c>
-      <c r="I13" s="42">
-        <v>30.0</v>
-      </c>
-      <c r="J13" s="61"/>
-      <c r="K13" s="24"/>
-    </row>
-    <row r="14">
+      <c r="F13" s="32">
+        <v>3</v>
+      </c>
+      <c r="G13" s="32">
+        <v>4</v>
+      </c>
+      <c r="H13" s="32">
+        <v>5</v>
+      </c>
+      <c r="I13" s="32">
+        <v>30</v>
+      </c>
+      <c r="J13" s="49"/>
+      <c r="K13" s="15"/>
+    </row>
+    <row r="14" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="57" t="s">
+      <c r="C14" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="59" t="s">
+      <c r="D14" s="47" t="s">
         <v>129</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="F14" s="42">
-        <v>0.0</v>
-      </c>
-      <c r="G14" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="H14" s="42">
+      <c r="F14" s="32">
+        <v>0</v>
+      </c>
+      <c r="G14" s="32">
+        <v>1</v>
+      </c>
+      <c r="H14" s="32">
         <v>2.5</v>
       </c>
-      <c r="I14" s="42">
-        <v>180.0</v>
-      </c>
-      <c r="J14" s="61"/>
-      <c r="K14" s="24"/>
-    </row>
-    <row r="15">
+      <c r="I14" s="32">
+        <v>180</v>
+      </c>
+      <c r="J14" s="49"/>
+      <c r="K14" s="15"/>
+    </row>
+    <row r="15" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="59" t="s">
+      <c r="B15" s="60"/>
+      <c r="C15" s="67"/>
+      <c r="D15" s="47" t="s">
         <v>134</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="F15" s="51">
-        <v>4.0</v>
-      </c>
-      <c r="G15" s="51">
-        <v>1.0</v>
-      </c>
-      <c r="H15" s="51">
-        <v>5.0</v>
-      </c>
-      <c r="I15" s="51">
-        <v>25.0</v>
-      </c>
-      <c r="J15" s="67"/>
-      <c r="K15" s="24"/>
-    </row>
-    <row r="16">
+      <c r="F15" s="41">
+        <v>4</v>
+      </c>
+      <c r="G15" s="41">
+        <v>1</v>
+      </c>
+      <c r="H15" s="41">
+        <v>5</v>
+      </c>
+      <c r="I15" s="41">
+        <v>25</v>
+      </c>
+      <c r="J15" s="53"/>
+      <c r="K15" s="15"/>
+    </row>
+    <row r="16" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="57" t="s">
+      <c r="C16" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="68" t="s">
+      <c r="D16" s="54" t="s">
         <v>135</v>
       </c>
-      <c r="E16" s="28" t="s">
+      <c r="E16" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G16" s="51">
-        <v>3.0</v>
-      </c>
-      <c r="H16" s="51">
-        <v>260.0</v>
-      </c>
-      <c r="I16" s="51"/>
-      <c r="J16" s="67"/>
-      <c r="K16" s="24"/>
-    </row>
-    <row r="17">
+      <c r="F16" s="41">
+        <v>0</v>
+      </c>
+      <c r="G16" s="41">
+        <v>3</v>
+      </c>
+      <c r="H16" s="41">
+        <v>260</v>
+      </c>
+      <c r="I16" s="41"/>
+      <c r="J16" s="53"/>
+      <c r="K16" s="15"/>
+    </row>
+    <row r="17" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
-      <c r="B17" s="62"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="68" t="s">
+      <c r="B17" s="69"/>
+      <c r="C17" s="71"/>
+      <c r="D17" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="F17" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G17" s="51">
-        <v>3.0</v>
-      </c>
-      <c r="H17" s="51">
-        <v>221.0</v>
-      </c>
-      <c r="I17" s="51"/>
-      <c r="J17" s="67"/>
-      <c r="K17" s="24"/>
-    </row>
-    <row r="18">
+      <c r="F17" s="41">
+        <v>0</v>
+      </c>
+      <c r="G17" s="41">
+        <v>3</v>
+      </c>
+      <c r="H17" s="41">
+        <v>221</v>
+      </c>
+      <c r="I17" s="41"/>
+      <c r="J17" s="53"/>
+      <c r="K17" s="15"/>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
-      <c r="B18" s="62"/>
-      <c r="C18" s="63"/>
-      <c r="D18" s="68" t="s">
+      <c r="B18" s="69"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="E18" s="28" t="s">
+      <c r="E18" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="F18" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G18" s="51">
-        <v>3.0</v>
-      </c>
-      <c r="H18" s="51">
-        <v>188.0</v>
-      </c>
-      <c r="I18" s="51"/>
-      <c r="J18" s="67"/>
-      <c r="K18" s="24"/>
-    </row>
-    <row r="19">
+      <c r="F18" s="41">
+        <v>0</v>
+      </c>
+      <c r="G18" s="41">
+        <v>3</v>
+      </c>
+      <c r="H18" s="41">
+        <v>188</v>
+      </c>
+      <c r="I18" s="41"/>
+      <c r="J18" s="53"/>
+      <c r="K18" s="15"/>
+    </row>
+    <row r="19" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
-      <c r="B19" s="62"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="68" t="s">
+      <c r="B19" s="69"/>
+      <c r="C19" s="71"/>
+      <c r="D19" s="54" t="s">
         <v>138</v>
       </c>
-      <c r="E19" s="28" t="s">
+      <c r="E19" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="F19" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G19" s="51">
-        <v>3.0</v>
-      </c>
-      <c r="H19" s="51">
-        <v>160.0</v>
-      </c>
-      <c r="I19" s="51"/>
-      <c r="J19" s="67"/>
-      <c r="K19" s="24"/>
-    </row>
-    <row r="20">
+      <c r="F19" s="41">
+        <v>0</v>
+      </c>
+      <c r="G19" s="41">
+        <v>3</v>
+      </c>
+      <c r="H19" s="41">
+        <v>160</v>
+      </c>
+      <c r="I19" s="41"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="15"/>
+    </row>
+    <row r="20" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="59" t="s">
+      <c r="B20" s="60"/>
+      <c r="C20" s="67"/>
+      <c r="D20" s="47" t="s">
         <v>139</v>
       </c>
-      <c r="E20" s="28" t="s">
+      <c r="E20" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="F20" s="51">
-        <v>5.0</v>
-      </c>
-      <c r="G20" s="51">
-        <v>2.0</v>
-      </c>
-      <c r="H20" s="51">
-        <v>30.0</v>
-      </c>
-      <c r="I20" s="51"/>
-      <c r="J20" s="67"/>
-      <c r="K20" s="24"/>
-    </row>
-    <row r="21">
+      <c r="F20" s="41">
+        <v>5</v>
+      </c>
+      <c r="G20" s="41">
+        <v>2</v>
+      </c>
+      <c r="H20" s="41">
+        <v>30</v>
+      </c>
+      <c r="I20" s="41"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="15"/>
+    </row>
+    <row r="21" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
-      <c r="B21" s="38" t="s">
+      <c r="B21" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="57" t="s">
+      <c r="C21" s="70" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="59" t="s">
+      <c r="D21" s="47" t="s">
         <v>140</v>
       </c>
-      <c r="E21" s="28" t="s">
+      <c r="E21" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="F21" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G21" s="51">
-        <v>1.0</v>
-      </c>
-      <c r="H21" s="51">
-        <v>2.0</v>
-      </c>
-      <c r="I21" s="51">
-        <v>220.0</v>
-      </c>
-      <c r="J21" s="67"/>
-      <c r="K21" s="24"/>
-    </row>
-    <row r="22">
+      <c r="F21" s="41">
+        <v>0</v>
+      </c>
+      <c r="G21" s="41">
+        <v>1</v>
+      </c>
+      <c r="H21" s="41">
+        <v>2</v>
+      </c>
+      <c r="I21" s="41">
+        <v>220</v>
+      </c>
+      <c r="J21" s="53"/>
+      <c r="K21" s="15"/>
+    </row>
+    <row r="22" spans="1:11" ht="24" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
-      <c r="B22" s="62"/>
-      <c r="C22" s="63"/>
-      <c r="D22" s="59" t="s">
+      <c r="B22" s="69"/>
+      <c r="C22" s="71"/>
+      <c r="D22" s="47" t="s">
         <v>141</v>
       </c>
-      <c r="E22" s="28" t="s">
+      <c r="E22" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="F22" s="51">
-        <v>6.0</v>
-      </c>
-      <c r="G22" s="51">
-        <v>1.0</v>
-      </c>
-      <c r="H22" s="51">
-        <v>30.0</v>
-      </c>
-      <c r="I22" s="51">
-        <v>120.0</v>
-      </c>
-      <c r="J22" s="67"/>
-      <c r="K22" s="24"/>
-    </row>
-    <row r="23">
+      <c r="F22" s="41">
+        <v>6</v>
+      </c>
+      <c r="G22" s="41">
+        <v>1</v>
+      </c>
+      <c r="H22" s="41">
+        <v>30</v>
+      </c>
+      <c r="I22" s="41">
+        <v>120</v>
+      </c>
+      <c r="J22" s="53"/>
+      <c r="K22" s="15"/>
+    </row>
+    <row r="23" spans="1:11" ht="24" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="59" t="s">
+      <c r="B23" s="60"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="E23" s="28" t="s">
+      <c r="E23" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="F23" s="51">
-        <v>5.0</v>
-      </c>
-      <c r="G23" s="51">
-        <v>2.0</v>
-      </c>
-      <c r="H23" s="51">
-        <v>30.0</v>
-      </c>
-      <c r="I23" s="51"/>
-      <c r="J23" s="67"/>
-      <c r="K23" s="24"/>
-    </row>
-    <row r="24">
+      <c r="F23" s="41">
+        <v>5</v>
+      </c>
+      <c r="G23" s="41">
+        <v>2</v>
+      </c>
+      <c r="H23" s="41">
+        <v>30</v>
+      </c>
+      <c r="I23" s="41"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="15"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
-      <c r="B24" s="38" t="s">
+      <c r="B24" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="C24" s="57" t="s">
+      <c r="C24" s="70" t="s">
         <v>79</v>
       </c>
-      <c r="D24" s="59" t="s">
+      <c r="D24" s="47" t="s">
         <v>143</v>
       </c>
-      <c r="E24" s="28" t="s">
+      <c r="E24" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F24" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G24" s="51">
-        <v>1.0</v>
-      </c>
-      <c r="H24" s="51">
+      <c r="F24" s="41">
+        <v>0</v>
+      </c>
+      <c r="G24" s="41">
+        <v>1</v>
+      </c>
+      <c r="H24" s="41">
         <v>2.5</v>
       </c>
-      <c r="I24" s="51">
-        <v>130.0</v>
-      </c>
-      <c r="J24" s="67"/>
-      <c r="K24" s="24"/>
-    </row>
-    <row r="25">
+      <c r="I24" s="41">
+        <v>130</v>
+      </c>
+      <c r="J24" s="53"/>
+      <c r="K24" s="15"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
-      <c r="B25" s="62"/>
-      <c r="C25" s="63"/>
-      <c r="D25" s="59" t="s">
+      <c r="B25" s="69"/>
+      <c r="C25" s="71"/>
+      <c r="D25" s="47" t="s">
         <v>144</v>
       </c>
-      <c r="E25" s="28" t="s">
+      <c r="E25" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F25" s="51">
-        <v>4.0</v>
-      </c>
-      <c r="G25" s="51">
-        <v>1.0</v>
-      </c>
-      <c r="H25" s="51">
+      <c r="F25" s="41">
+        <v>4</v>
+      </c>
+      <c r="G25" s="41">
+        <v>1</v>
+      </c>
+      <c r="H25" s="41">
         <v>1.5</v>
       </c>
-      <c r="I25" s="51"/>
-      <c r="J25" s="67"/>
-      <c r="K25" s="24"/>
-    </row>
-    <row r="26">
+      <c r="I25" s="41"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="15"/>
+    </row>
+    <row r="26" spans="1:11" ht="24" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
-      <c r="B26" s="62"/>
-      <c r="C26" s="63"/>
-      <c r="D26" s="59" t="s">
+      <c r="B26" s="69"/>
+      <c r="C26" s="71"/>
+      <c r="D26" s="47" t="s">
         <v>145</v>
       </c>
-      <c r="E26" s="28" t="s">
+      <c r="E26" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F26" s="51">
-        <v>4.0</v>
-      </c>
-      <c r="G26" s="51">
-        <v>1.0</v>
-      </c>
-      <c r="H26" s="51">
-        <v>4.0</v>
-      </c>
-      <c r="I26" s="51">
-        <v>35.0</v>
-      </c>
-      <c r="J26" s="67"/>
-      <c r="K26" s="24"/>
-    </row>
-    <row r="27">
+      <c r="F26" s="41">
+        <v>4</v>
+      </c>
+      <c r="G26" s="41">
+        <v>1</v>
+      </c>
+      <c r="H26" s="41">
+        <v>4</v>
+      </c>
+      <c r="I26" s="41">
+        <v>35</v>
+      </c>
+      <c r="J26" s="53"/>
+      <c r="K26" s="15"/>
+    </row>
+    <row r="27" spans="1:11" ht="24" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
-      <c r="B27" s="62"/>
-      <c r="C27" s="63"/>
-      <c r="D27" s="59" t="s">
+      <c r="B27" s="69"/>
+      <c r="C27" s="71"/>
+      <c r="D27" s="47" t="s">
         <v>146</v>
       </c>
-      <c r="E27" s="28" t="s">
+      <c r="E27" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F27" s="51">
-        <v>4.0</v>
-      </c>
-      <c r="G27" s="51">
-        <v>1.0</v>
-      </c>
-      <c r="H27" s="51">
-        <v>4.0</v>
-      </c>
-      <c r="I27" s="51">
-        <v>35.0</v>
-      </c>
-      <c r="J27" s="67"/>
-      <c r="K27" s="24"/>
-    </row>
-    <row r="28">
+      <c r="F27" s="41">
+        <v>4</v>
+      </c>
+      <c r="G27" s="41">
+        <v>1</v>
+      </c>
+      <c r="H27" s="41">
+        <v>4</v>
+      </c>
+      <c r="I27" s="41">
+        <v>35</v>
+      </c>
+      <c r="J27" s="53"/>
+      <c r="K27" s="15"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="59" t="s">
+      <c r="B28" s="60"/>
+      <c r="C28" s="67"/>
+      <c r="D28" s="47" t="s">
         <v>139</v>
       </c>
-      <c r="E28" s="28" t="s">
+      <c r="E28" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F28" s="51">
-        <v>5.0</v>
-      </c>
-      <c r="G28" s="51">
-        <v>2.0</v>
-      </c>
-      <c r="H28" s="51">
-        <v>30.0</v>
-      </c>
-      <c r="I28" s="51"/>
-      <c r="J28" s="67"/>
-      <c r="K28" s="24"/>
-    </row>
-    <row r="29">
+      <c r="F28" s="41">
+        <v>5</v>
+      </c>
+      <c r="G28" s="41">
+        <v>2</v>
+      </c>
+      <c r="H28" s="41">
+        <v>30</v>
+      </c>
+      <c r="I28" s="41"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="15"/>
+    </row>
+    <row r="29" spans="1:11" ht="24" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
-      <c r="B29" s="38" t="s">
+      <c r="B29" s="68" t="s">
         <v>82</v>
       </c>
-      <c r="C29" s="57" t="s">
+      <c r="C29" s="70" t="s">
         <v>83</v>
       </c>
-      <c r="D29" s="59" t="s">
+      <c r="D29" s="47" t="s">
         <v>147</v>
       </c>
-      <c r="E29" s="28" t="s">
+      <c r="E29" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="F29" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G29" s="51">
-        <v>3.0</v>
-      </c>
-      <c r="H29" s="51">
-        <v>5.0</v>
-      </c>
-      <c r="I29" s="51">
-        <v>5.0</v>
-      </c>
-      <c r="J29" s="67"/>
-      <c r="K29" s="24"/>
-    </row>
-    <row r="30">
+      <c r="F29" s="41">
+        <v>0</v>
+      </c>
+      <c r="G29" s="41">
+        <v>3</v>
+      </c>
+      <c r="H29" s="41">
+        <v>5</v>
+      </c>
+      <c r="I29" s="41">
+        <v>5</v>
+      </c>
+      <c r="J29" s="53"/>
+      <c r="K29" s="15"/>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
-      <c r="B30" s="62"/>
-      <c r="C30" s="63"/>
-      <c r="D30" s="59" t="s">
+      <c r="B30" s="69"/>
+      <c r="C30" s="71"/>
+      <c r="D30" s="47" t="s">
         <v>148</v>
       </c>
-      <c r="E30" s="28" t="s">
+      <c r="E30" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="F30" s="51">
-        <v>7.0</v>
-      </c>
-      <c r="G30" s="51">
-        <v>3.0</v>
-      </c>
-      <c r="H30" s="51">
+      <c r="F30" s="41">
+        <v>7</v>
+      </c>
+      <c r="G30" s="41">
+        <v>3</v>
+      </c>
+      <c r="H30" s="41">
         <v>1.5</v>
       </c>
-      <c r="I30" s="51"/>
-      <c r="J30" s="67"/>
-      <c r="K30" s="24"/>
-    </row>
-    <row r="31">
+      <c r="I30" s="41"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="15"/>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
-      <c r="B31" s="62"/>
-      <c r="C31" s="63"/>
-      <c r="D31" s="59" t="s">
+      <c r="B31" s="69"/>
+      <c r="C31" s="71"/>
+      <c r="D31" s="47" t="s">
         <v>149</v>
       </c>
-      <c r="E31" s="28" t="s">
+      <c r="E31" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="F31" s="51">
-        <v>7.0</v>
-      </c>
-      <c r="G31" s="51">
-        <v>3.0</v>
-      </c>
-      <c r="H31" s="51">
-        <v>200.0</v>
-      </c>
-      <c r="I31" s="51"/>
-      <c r="J31" s="67"/>
-      <c r="K31" s="24"/>
-    </row>
-    <row r="32">
+      <c r="F31" s="41">
+        <v>7</v>
+      </c>
+      <c r="G31" s="41">
+        <v>3</v>
+      </c>
+      <c r="H31" s="41">
+        <v>200</v>
+      </c>
+      <c r="I31" s="41"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="15"/>
+    </row>
+    <row r="32" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="68" t="s">
+      <c r="B32" s="60"/>
+      <c r="C32" s="67"/>
+      <c r="D32" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="E32" s="28" t="s">
+      <c r="E32" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="F32" s="51">
-        <v>3.0</v>
-      </c>
-      <c r="G32" s="51">
-        <v>4.0</v>
-      </c>
-      <c r="H32" s="51"/>
-      <c r="I32" s="51"/>
-      <c r="J32" s="67"/>
-      <c r="K32" s="24"/>
-    </row>
-    <row r="33">
+      <c r="F32" s="41">
+        <v>3</v>
+      </c>
+      <c r="G32" s="41">
+        <v>4</v>
+      </c>
+      <c r="H32" s="41"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="15"/>
+    </row>
+    <row r="33" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
-      <c r="B33" s="38" t="s">
+      <c r="B33" s="68" t="s">
         <v>86</v>
       </c>
-      <c r="C33" s="57" t="s">
+      <c r="C33" s="70" t="s">
         <v>89</v>
       </c>
-      <c r="D33" s="68" t="s">
+      <c r="D33" s="54" t="s">
         <v>151</v>
       </c>
-      <c r="E33" s="28" t="s">
+      <c r="E33" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="F33" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G33" s="51">
-        <v>3.0</v>
-      </c>
-      <c r="H33" s="51">
-        <v>140.0</v>
-      </c>
-      <c r="I33" s="51"/>
-      <c r="J33" s="69"/>
-      <c r="K33" s="24"/>
-    </row>
-    <row r="34">
+      <c r="F33" s="41">
+        <v>0</v>
+      </c>
+      <c r="G33" s="41">
+        <v>3</v>
+      </c>
+      <c r="H33" s="41">
+        <v>140</v>
+      </c>
+      <c r="I33" s="41"/>
+      <c r="J33" s="55"/>
+      <c r="K33" s="15"/>
+    </row>
+    <row r="34" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
-      <c r="B34" s="62"/>
-      <c r="C34" s="63"/>
-      <c r="D34" s="59" t="s">
+      <c r="B34" s="69"/>
+      <c r="C34" s="71"/>
+      <c r="D34" s="47" t="s">
         <v>152</v>
       </c>
-      <c r="E34" s="28" t="s">
+      <c r="E34" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="F34" s="51">
-        <v>0.0</v>
-      </c>
-      <c r="G34" s="51">
-        <v>3.0</v>
-      </c>
-      <c r="H34" s="51">
-        <v>140.0</v>
-      </c>
-      <c r="I34" s="51"/>
-      <c r="J34" s="69"/>
-      <c r="K34" s="24"/>
-    </row>
-    <row r="35">
+      <c r="F34" s="41">
+        <v>0</v>
+      </c>
+      <c r="G34" s="41">
+        <v>3</v>
+      </c>
+      <c r="H34" s="41">
+        <v>140</v>
+      </c>
+      <c r="I34" s="41"/>
+      <c r="J34" s="55"/>
+      <c r="K34" s="15"/>
+    </row>
+    <row r="35" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="62"/>
-      <c r="C35" s="63"/>
-      <c r="D35" s="59" t="s">
+      <c r="B35" s="69"/>
+      <c r="C35" s="71"/>
+      <c r="D35" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="E35" s="28" t="s">
+      <c r="E35" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="F35" s="51">
-        <v>4.0</v>
-      </c>
-      <c r="G35" s="51">
-        <v>3.0</v>
-      </c>
-      <c r="H35" s="51">
-        <v>1.0</v>
-      </c>
-      <c r="I35" s="51"/>
-      <c r="J35" s="69"/>
-      <c r="K35" s="24"/>
-    </row>
-    <row r="36">
+      <c r="F35" s="41">
+        <v>4</v>
+      </c>
+      <c r="G35" s="41">
+        <v>3</v>
+      </c>
+      <c r="H35" s="41">
+        <v>1</v>
+      </c>
+      <c r="I35" s="41"/>
+      <c r="J35" s="55"/>
+      <c r="K35" s="15"/>
+    </row>
+    <row r="36" spans="1:11" ht="24" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="62"/>
-      <c r="C36" s="63"/>
-      <c r="D36" s="59" t="s">
+      <c r="B36" s="69"/>
+      <c r="C36" s="71"/>
+      <c r="D36" s="47" t="s">
         <v>154</v>
       </c>
-      <c r="E36" s="28" t="s">
+      <c r="E36" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="F36" s="51">
-        <v>3.0</v>
-      </c>
-      <c r="G36" s="51">
-        <v>5.0</v>
-      </c>
-      <c r="H36" s="51">
+      <c r="F36" s="41">
+        <v>3</v>
+      </c>
+      <c r="G36" s="41">
+        <v>5</v>
+      </c>
+      <c r="H36" s="41">
         <v>2.5</v>
       </c>
-      <c r="I36" s="51">
-        <v>5.0</v>
-      </c>
-      <c r="J36" s="69">
-        <v>20.0</v>
-      </c>
-      <c r="K36" s="24"/>
-    </row>
-    <row r="37">
+      <c r="I36" s="41">
+        <v>5</v>
+      </c>
+      <c r="J36" s="55">
+        <v>20</v>
+      </c>
+      <c r="K36" s="15"/>
+    </row>
+    <row r="37" spans="1:11" ht="24" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="59" t="s">
+      <c r="B37" s="60"/>
+      <c r="C37" s="67"/>
+      <c r="D37" s="47" t="s">
         <v>155</v>
       </c>
-      <c r="E37" s="31" t="s">
+      <c r="E37" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="F37" s="58">
-        <v>3.0</v>
-      </c>
-      <c r="G37" s="58">
-        <v>5.0</v>
-      </c>
-      <c r="H37" s="58">
+      <c r="F37" s="46">
+        <v>3</v>
+      </c>
+      <c r="G37" s="46">
+        <v>5</v>
+      </c>
+      <c r="H37" s="46">
         <v>2.5</v>
       </c>
-      <c r="I37" s="58">
-        <v>5.0</v>
-      </c>
-      <c r="J37" s="70"/>
-      <c r="K37" s="24"/>
-    </row>
-    <row r="38">
+      <c r="I37" s="46">
+        <v>5</v>
+      </c>
+      <c r="J37" s="56"/>
+      <c r="K37" s="15"/>
+    </row>
+    <row r="38" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
-      <c r="B38" s="33"/>
-      <c r="C38" s="33"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="34"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
-      <c r="K38" s="34"/>
+      <c r="K38" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
     <mergeCell ref="B29:B32"/>
     <mergeCell ref="C29:C32"/>
     <mergeCell ref="C33:C37"/>
@@ -3929,20 +4039,15 @@
     <mergeCell ref="C21:C23"/>
     <mergeCell ref="B24:B28"/>
     <mergeCell ref="C24:C28"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="C14:C15"/>
   </mergeCells>
-  <printOptions gridLines="1" horizontalCentered="1"/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup fitToHeight="0" paperSize="9" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <printOptions horizontalCentered="1" gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
 </worksheet>
 </file>